--- a/evaluations/count/population_counting_results_ensamble.xlsx
+++ b/evaluations/count/population_counting_results_ensamble.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,7 +599,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -611,25 +611,25 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>2500</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>2500</v>
       </c>
       <c r="F3" t="n">
-        <v>2500</v>
+        <v>6250000</v>
       </c>
       <c r="G3" t="n">
-        <v>2500</v>
+        <v>6250000</v>
       </c>
       <c r="H3" t="n">
-        <v>817</v>
+        <v>212936</v>
       </c>
       <c r="I3" t="n">
-        <v>817</v>
+        <v>212936</v>
       </c>
       <c r="J3" t="n">
-        <v>817</v>
+        <v>212936</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -641,31 +641,31 @@
         <v>256</v>
       </c>
       <c r="N3" t="n">
-        <v>2000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.75</v>
+        <v>0.998</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>33.56</v>
+        <v>280.67</v>
       </c>
       <c r="R3" t="n">
-        <v>5.42</v>
+        <v>10.05</v>
       </c>
       <c r="S3" t="n">
-        <v>105.15</v>
+        <v>1119.74</v>
       </c>
       <c r="T3" t="n">
-        <v>13</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -677,25 +677,25 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="n">
-        <v>2500</v>
+        <v>1000000</v>
       </c>
       <c r="G4" t="n">
-        <v>2500</v>
+        <v>1000000</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>69357</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>69357</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>69357</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -707,31 +707,31 @@
         <v>256</v>
       </c>
       <c r="N4" t="n">
-        <v>2000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.75</v>
+        <v>0.995</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4023.78</v>
+        <v>226.2</v>
       </c>
       <c r="R4" t="n">
-        <v>363</v>
+        <v>11.53</v>
       </c>
       <c r="S4" t="n">
-        <v>61.6</v>
+        <v>182.6</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -743,25 +743,25 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>2500</v>
+        <v>250000</v>
       </c>
       <c r="G5" t="n">
-        <v>2500</v>
+        <v>250000</v>
       </c>
       <c r="H5" t="n">
-        <v>56</v>
+        <v>24747</v>
       </c>
       <c r="I5" t="n">
-        <v>56</v>
+        <v>24747</v>
       </c>
       <c r="J5" t="n">
-        <v>56</v>
+        <v>24747</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -773,31 +773,31 @@
         <v>256</v>
       </c>
       <c r="N5" t="n">
-        <v>2000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="O5" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>783.6799999999999</v>
+        <v>169.89</v>
       </c>
       <c r="R5" t="n">
-        <v>96.36</v>
+        <v>12.22</v>
       </c>
       <c r="S5" t="n">
-        <v>30.65</v>
+        <v>47.27</v>
       </c>
       <c r="T5" t="n">
-        <v>237</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -809,25 +809,25 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>2500</v>
+        <v>250000</v>
       </c>
       <c r="G6" t="n">
-        <v>2500</v>
+        <v>250000</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>20137</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>20137</v>
       </c>
       <c r="J6" t="n">
-        <v>35</v>
+        <v>20137</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>256</v>
       </c>
       <c r="N6" t="n">
-        <v>2000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="O6" t="n">
         <v>0.75</v>
@@ -848,16 +848,4834 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>279.29</v>
+      </c>
+      <c r="R6" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="T6" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E7" t="n">
+        <v>250</v>
+      </c>
+      <c r="F7" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G7" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6944</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6944</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6944</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>256</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>179.45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="T7" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>250</v>
+      </c>
+      <c r="E8" t="n">
+        <v>250</v>
+      </c>
+      <c r="F8" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G8" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7801</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7801</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7801</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>256</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>159.21</v>
+      </c>
+      <c r="R8" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="T8" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>700</v>
+      </c>
+      <c r="E9" t="n">
+        <v>700</v>
+      </c>
+      <c r="F9" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G9" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>40996</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40996</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40996</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>256</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>181.07</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="S9" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="T9" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77480</v>
+      </c>
+      <c r="I10" t="n">
+        <v>77480</v>
+      </c>
+      <c r="J10" t="n">
+        <v>77480</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>256</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>225.84</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>220.37</v>
+      </c>
+      <c r="T10" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7568</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7568</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7568</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>256</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>299.24</v>
+      </c>
+      <c r="R11" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>256</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5479.89</v>
+      </c>
+      <c r="R12" t="n">
+        <v>398.11</v>
+      </c>
+      <c r="S12" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>500</v>
+      </c>
+      <c r="F13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3386</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3386</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3386</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>256</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1820.69</v>
+      </c>
+      <c r="R13" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="S13" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="T13" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E14" t="n">
+        <v>250</v>
+      </c>
+      <c r="F14" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G14" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H14" t="n">
+        <v>836</v>
+      </c>
+      <c r="I14" t="n">
+        <v>836</v>
+      </c>
+      <c r="J14" t="n">
+        <v>836</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>256</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2540.86</v>
+      </c>
+      <c r="R14" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>13</v>
+      </c>
+      <c r="T14" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10654</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10654</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10654</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>256</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1729.56</v>
+      </c>
+      <c r="R15" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="S15" t="n">
+        <v>193.37</v>
+      </c>
+      <c r="T15" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E16" t="n">
+        <v>500</v>
+      </c>
+      <c r="F16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>576</v>
+      </c>
+      <c r="I16" t="n">
+        <v>576</v>
+      </c>
+      <c r="J16" t="n">
+        <v>576</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>256</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4480.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>112.22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>700</v>
+      </c>
+      <c r="E17" t="n">
+        <v>700</v>
+      </c>
+      <c r="F17" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5962</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5962</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5962</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>256</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1782.81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="S17" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="T17" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>250</v>
+      </c>
+      <c r="E18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F18" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G18" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H18" t="n">
+        <v>306</v>
+      </c>
+      <c r="I18" t="n">
+        <v>306</v>
+      </c>
+      <c r="J18" t="n">
+        <v>306</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>256</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3935</v>
+      </c>
+      <c r="R18" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="S18" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="T18" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>747</v>
+      </c>
+      <c r="I19" t="n">
+        <v>747</v>
+      </c>
+      <c r="J19" t="n">
+        <v>747</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>256</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4118.22</v>
+      </c>
+      <c r="R19" t="n">
+        <v>109.77</v>
+      </c>
+      <c r="S19" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="T19" t="n">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1038361</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1038361</v>
+      </c>
+      <c r="H20" t="n">
+        <v>66921</v>
+      </c>
+      <c r="I20" t="n">
+        <v>66921</v>
+      </c>
+      <c r="J20" t="n">
+        <v>66921</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>256</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>219.58</v>
+      </c>
+      <c r="T20" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>65345</v>
+      </c>
+      <c r="I21" t="n">
+        <v>65345</v>
+      </c>
+      <c r="J21" t="n">
+        <v>65345</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>256</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S21" t="n">
+        <v>211.16</v>
+      </c>
+      <c r="T21" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>16665</v>
+      </c>
+      <c r="I22" t="n">
+        <v>16665</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16665</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>256</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="T22" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>250</v>
+      </c>
+      <c r="E23" t="n">
+        <v>250</v>
+      </c>
+      <c r="F23" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G23" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11934</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11934</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11934</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>256</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S23" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="T23" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>500</v>
+      </c>
+      <c r="E24" t="n">
+        <v>500</v>
+      </c>
+      <c r="F24" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28792</v>
+      </c>
+      <c r="I24" t="n">
+        <v>28792</v>
+      </c>
+      <c r="J24" t="n">
+        <v>28792</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>256</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S24" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1038361</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1038361</v>
+      </c>
+      <c r="H25" t="n">
+        <v>66921</v>
+      </c>
+      <c r="I25" t="n">
+        <v>66921</v>
+      </c>
+      <c r="J25" t="n">
+        <v>66921</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>256</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>218.19</v>
+      </c>
+      <c r="T25" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H26" t="n">
+        <v>817</v>
+      </c>
+      <c r="I26" t="n">
+        <v>817</v>
+      </c>
+      <c r="J26" t="n">
+        <v>817</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>256</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="S26" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>700</v>
+      </c>
+      <c r="E27" t="n">
+        <v>700</v>
+      </c>
+      <c r="F27" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>42281</v>
+      </c>
+      <c r="I27" t="n">
+        <v>42281</v>
+      </c>
+      <c r="J27" t="n">
+        <v>42281</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>256</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S27" t="n">
+        <v>104.17</v>
+      </c>
+      <c r="T27" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>250</v>
+      </c>
+      <c r="E28" t="n">
+        <v>250</v>
+      </c>
+      <c r="F28" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G28" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10685</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10685</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10685</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>256</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="S28" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="T28" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E29" t="n">
+        <v>500</v>
+      </c>
+      <c r="F29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24516</v>
+      </c>
+      <c r="I29" t="n">
+        <v>24516</v>
+      </c>
+      <c r="J29" t="n">
+        <v>24516</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>256</v>
+      </c>
+      <c r="N29" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="T29" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>250</v>
+      </c>
+      <c r="E30" t="n">
+        <v>250</v>
+      </c>
+      <c r="F30" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G30" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1216</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1216</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1216</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>256</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>333.59</v>
+      </c>
+      <c r="R30" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="T30" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>820836</v>
+      </c>
+      <c r="G31" t="n">
+        <v>820836</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6726</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6726</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6726</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>256</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>148.74</v>
+      </c>
+      <c r="T31" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H32" t="n">
+        <v>86</v>
+      </c>
+      <c r="I32" t="n">
+        <v>86</v>
+      </c>
+      <c r="J32" t="n">
+        <v>86</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>256</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>443.11</v>
+      </c>
+      <c r="R32" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="S32" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="T32" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>250</v>
+      </c>
+      <c r="E33" t="n">
+        <v>250</v>
+      </c>
+      <c r="F33" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G33" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1007</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1007</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1007</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>256</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>403.31</v>
+      </c>
+      <c r="R33" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="S33" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="T33" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>500</v>
+      </c>
+      <c r="E34" t="n">
+        <v>500</v>
+      </c>
+      <c r="F34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2159</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2159</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2159</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>256</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>465.86</v>
+      </c>
+      <c r="R34" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="S34" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="T34" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>700</v>
+      </c>
+      <c r="E35" t="n">
+        <v>700</v>
+      </c>
+      <c r="F35" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4502</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4502</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4502</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>256</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>205.18</v>
+      </c>
+      <c r="R35" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="S35" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="T35" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>500</v>
+      </c>
+      <c r="E36" t="n">
+        <v>500</v>
+      </c>
+      <c r="F36" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3065</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3065</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3065</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>256</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>332.54</v>
+      </c>
+      <c r="R36" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="S36" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="T36" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" t="n">
+        <v>45300</v>
+      </c>
+      <c r="G37" t="n">
+        <v>45300</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1931</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1931</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1931</v>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>256</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>341.25</v>
+      </c>
+      <c r="R37" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="T37" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>700</v>
+      </c>
+      <c r="E38" t="n">
+        <v>700</v>
+      </c>
+      <c r="F38" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2569</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2569</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2569</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>256</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1338.02</v>
+      </c>
+      <c r="R38" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="S38" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="T38" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>697</v>
+      </c>
+      <c r="I39" t="n">
+        <v>697</v>
+      </c>
+      <c r="J39" t="n">
+        <v>697</v>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>256</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1740.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="T39" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>500</v>
+      </c>
+      <c r="E40" t="n">
+        <v>500</v>
+      </c>
+      <c r="F40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1785</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1785</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1785</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>256</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1281.6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="S40" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="T40" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C41" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>250</v>
+      </c>
+      <c r="E41" t="n">
+        <v>250</v>
+      </c>
+      <c r="F41" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G41" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H41" t="n">
+        <v>552</v>
+      </c>
+      <c r="I41" t="n">
+        <v>552</v>
+      </c>
+      <c r="J41" t="n">
+        <v>552</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>256</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1385.98</v>
+      </c>
+      <c r="R41" t="n">
+        <v>66.39</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="T41" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>50</v>
+      </c>
+      <c r="E42" t="n">
+        <v>50</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H42" t="n">
+        <v>35</v>
+      </c>
+      <c r="I42" t="n">
+        <v>35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>35</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>256</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1696.83</v>
+      </c>
+      <c r="R42" t="n">
+        <v>160.03</v>
+      </c>
+      <c r="S42" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="T42" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>250</v>
+      </c>
+      <c r="E43" t="n">
+        <v>250</v>
+      </c>
+      <c r="F43" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G43" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H43" t="n">
+        <v>599</v>
+      </c>
+      <c r="I43" t="n">
+        <v>599</v>
+      </c>
+      <c r="J43" t="n">
+        <v>599</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>256</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1236.46</v>
+      </c>
+      <c r="R43" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>500</v>
+      </c>
+      <c r="E44" t="n">
+        <v>500</v>
+      </c>
+      <c r="F44" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1276</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1276</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1276</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>256</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1506.05</v>
+      </c>
+      <c r="R44" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="S44" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="T44" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4454</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4454</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4454</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>256</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1330.07</v>
+      </c>
+      <c r="R45" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="S45" t="n">
+        <v>152.96</v>
+      </c>
+      <c r="T45" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C46" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H46" t="n">
+        <v>20</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" t="n">
+        <v>20</v>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>256</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4023.78</v>
+      </c>
+      <c r="R46" t="n">
+        <v>363</v>
+      </c>
+      <c r="S46" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C47" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>700</v>
+      </c>
+      <c r="E47" t="n">
+        <v>700</v>
+      </c>
+      <c r="F47" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>9381</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9381</v>
+      </c>
+      <c r="J47" t="n">
+        <v>9381</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>256</v>
+      </c>
+      <c r="N47" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>711.5599999999999</v>
+      </c>
+      <c r="R47" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="S47" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="T47" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C48" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>250</v>
+      </c>
+      <c r="E48" t="n">
+        <v>250</v>
+      </c>
+      <c r="F48" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G48" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1328</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1328</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1328</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>256</v>
+      </c>
+      <c r="N48" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>994.34</v>
+      </c>
+      <c r="R48" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="S48" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="T48" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1051</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1051</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1051</v>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>256</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2724.62</v>
+      </c>
+      <c r="R49" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="S49" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="T49" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>250</v>
+      </c>
+      <c r="E50" t="n">
+        <v>250</v>
+      </c>
+      <c r="F50" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G50" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H50" t="n">
+        <v>633</v>
+      </c>
+      <c r="I50" t="n">
+        <v>633</v>
+      </c>
+      <c r="J50" t="n">
+        <v>633</v>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>256</v>
+      </c>
+      <c r="N50" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2212.8</v>
+      </c>
+      <c r="R50" t="n">
+        <v>156.77</v>
+      </c>
+      <c r="S50" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="T50" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>500</v>
+      </c>
+      <c r="E51" t="n">
+        <v>500</v>
+      </c>
+      <c r="F51" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1644</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1644</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>256</v>
+      </c>
+      <c r="N51" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2179.76</v>
+      </c>
+      <c r="R51" t="n">
+        <v>91.86</v>
+      </c>
+      <c r="S51" t="n">
+        <v>61.26</v>
+      </c>
+      <c r="T51" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C52" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>500</v>
+      </c>
+      <c r="E52" t="n">
+        <v>500</v>
+      </c>
+      <c r="F52" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4647</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4647</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4647</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>256</v>
+      </c>
+      <c r="N52" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>764.3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="S52" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="T52" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C53" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>16869</v>
+      </c>
+      <c r="I53" t="n">
+        <v>16869</v>
+      </c>
+      <c r="J53" t="n">
+        <v>16869</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>256</v>
+      </c>
+      <c r="N53" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>643.8200000000001</v>
+      </c>
+      <c r="R53" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="S53" t="n">
+        <v>240.36</v>
+      </c>
+      <c r="T53" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C54" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="H54" t="n">
+        <v>19868</v>
+      </c>
+      <c r="I54" t="n">
+        <v>19868</v>
+      </c>
+      <c r="J54" t="n">
+        <v>19868</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>256</v>
+      </c>
+      <c r="N54" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>622.42</v>
+      </c>
+      <c r="R54" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="S54" t="n">
+        <v>289.97</v>
+      </c>
+      <c r="T54" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C55" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>500</v>
+      </c>
+      <c r="E55" t="n">
+        <v>500</v>
+      </c>
+      <c r="F55" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3227</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3227</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3227</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>256</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>565.9299999999999</v>
+      </c>
+      <c r="R55" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="S55" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="T55" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C56" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>700</v>
+      </c>
+      <c r="E56" t="n">
+        <v>700</v>
+      </c>
+      <c r="F56" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H56" t="n">
+        <v>7797</v>
+      </c>
+      <c r="I56" t="n">
+        <v>7797</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7797</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>256</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="R56" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="S56" t="n">
+        <v>96.26000000000001</v>
+      </c>
+      <c r="T56" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H57" t="n">
+        <v>56</v>
+      </c>
+      <c r="I57" t="n">
+        <v>56</v>
+      </c>
+      <c r="J57" t="n">
+        <v>56</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>256</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>783.6799999999999</v>
+      </c>
+      <c r="R57" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="S57" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="T57" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>50</v>
+      </c>
+      <c r="F58" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1622</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1622</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1622</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>256</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>615.13</v>
+      </c>
+      <c r="R58" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="T58" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C59" t="b">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>500</v>
+      </c>
+      <c r="E59" t="n">
+        <v>500</v>
+      </c>
+      <c r="F59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H59" t="n">
+        <v>5052</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5052</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5052</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>256</v>
+      </c>
+      <c r="N59" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="S59" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="T59" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="H60" t="n">
+        <v>13469</v>
+      </c>
+      <c r="I60" t="n">
+        <v>13469</v>
+      </c>
+      <c r="J60" t="n">
+        <v>13469</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>256</v>
+      </c>
+      <c r="N60" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>229.82</v>
+      </c>
+      <c r="R60" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="S60" t="n">
+        <v>238.18</v>
+      </c>
+      <c r="T60" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>250</v>
+      </c>
+      <c r="E61" t="n">
+        <v>250</v>
+      </c>
+      <c r="F61" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G61" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1640</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1640</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1640</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>256</v>
+      </c>
+      <c r="N61" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>348.61</v>
+      </c>
+      <c r="R61" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="S61" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="T61" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>250</v>
+      </c>
+      <c r="E62" t="n">
+        <v>250</v>
+      </c>
+      <c r="F62" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G62" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1277</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1277</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1277</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>256</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>457.3</v>
+      </c>
+      <c r="R62" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="S62" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="T62" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C63" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H63" t="n">
+        <v>11700</v>
+      </c>
+      <c r="I63" t="n">
+        <v>11700</v>
+      </c>
+      <c r="J63" t="n">
+        <v>11700</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>256</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>285.61</v>
+      </c>
+      <c r="R63" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="S63" t="n">
+        <v>196.93</v>
+      </c>
+      <c r="T63" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C64" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>500</v>
+      </c>
+      <c r="E64" t="n">
+        <v>500</v>
+      </c>
+      <c r="F64" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H64" t="n">
+        <v>5114</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5114</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5114</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>256</v>
+      </c>
+      <c r="N64" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>284.29</v>
+      </c>
+      <c r="R64" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S64" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="T64" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C65" t="b">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>250</v>
+      </c>
+      <c r="E65" t="n">
+        <v>250</v>
+      </c>
+      <c r="F65" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G65" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H65" t="n">
+        <v>744</v>
+      </c>
+      <c r="I65" t="n">
+        <v>744</v>
+      </c>
+      <c r="J65" t="n">
+        <v>744</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>256</v>
+      </c>
+      <c r="N65" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>645.55</v>
+      </c>
+      <c r="R65" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="S65" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="T65" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C66" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>700</v>
+      </c>
+      <c r="E66" t="n">
+        <v>700</v>
+      </c>
+      <c r="F66" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>9670</v>
+      </c>
+      <c r="I66" t="n">
+        <v>9670</v>
+      </c>
+      <c r="J66" t="n">
+        <v>9670</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>256</v>
+      </c>
+      <c r="N66" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>258.81</v>
+      </c>
+      <c r="R66" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="S66" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="T66" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C67" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>250</v>
+      </c>
+      <c r="E67" t="n">
+        <v>250</v>
+      </c>
+      <c r="F67" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G67" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1634</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1634</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1634</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>256</v>
+      </c>
+      <c r="N67" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>297.21</v>
+      </c>
+      <c r="R67" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="S67" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="T67" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>500</v>
+      </c>
+      <c r="E68" t="n">
+        <v>500</v>
+      </c>
+      <c r="F68" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1592</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1592</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1592</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>256</v>
+      </c>
+      <c r="N68" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>738.14</v>
+      </c>
+      <c r="R68" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="S68" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="T68" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C69" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>50</v>
+      </c>
+      <c r="E69" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H69" t="n">
+        <v>35</v>
+      </c>
+      <c r="I69" t="n">
+        <v>35</v>
+      </c>
+      <c r="J69" t="n">
+        <v>35</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>256</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
         <v>895.02</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R69" t="n">
         <v>92.94</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S69" t="n">
         <v>37.42</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T69" t="n">
         <v>57</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1563</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1563</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1563</v>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>256</v>
+      </c>
+      <c r="N70" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>700.3099999999999</v>
+      </c>
+      <c r="R70" t="n">
+        <v>25</v>
+      </c>
+      <c r="S70" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="T70" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>16581</v>
+      </c>
+      <c r="I71" t="n">
+        <v>16581</v>
+      </c>
+      <c r="J71" t="n">
+        <v>16581</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>256</v>
+      </c>
+      <c r="N71" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>209.56</v>
+      </c>
+      <c r="R71" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="S71" t="n">
+        <v>164.05</v>
+      </c>
+      <c r="T71" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F72" t="n">
+        <v>429025</v>
+      </c>
+      <c r="G72" t="n">
+        <v>429025</v>
+      </c>
+      <c r="H72" t="n">
+        <v>7483</v>
+      </c>
+      <c r="I72" t="n">
+        <v>7483</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7483</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>256</v>
+      </c>
+      <c r="N72" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="T72" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>250</v>
+      </c>
+      <c r="E73" t="n">
+        <v>250</v>
+      </c>
+      <c r="F73" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G73" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2509</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2509</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2509</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>256</v>
+      </c>
+      <c r="N73" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="R73" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="S73" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="T73" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E74" t="n">
+        <v>50</v>
+      </c>
+      <c r="F74" t="n">
+        <v>32750</v>
+      </c>
+      <c r="G74" t="n">
+        <v>32750</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4112</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4112</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4112</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>256</v>
+      </c>
+      <c r="N74" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>136.02</v>
+      </c>
+      <c r="R74" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T74" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>500</v>
+      </c>
+      <c r="E75" t="n">
+        <v>500</v>
+      </c>
+      <c r="F75" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G75" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H75" t="n">
+        <v>5383</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5383</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5383</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>256</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="R75" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="S75" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="T75" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>700</v>
+      </c>
+      <c r="E76" t="n">
+        <v>700</v>
+      </c>
+      <c r="F76" t="n">
+        <v>429025</v>
+      </c>
+      <c r="G76" t="n">
+        <v>429025</v>
+      </c>
+      <c r="H76" t="n">
+        <v>7483</v>
+      </c>
+      <c r="I76" t="n">
+        <v>7483</v>
+      </c>
+      <c r="J76" t="n">
+        <v>7483</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>256</v>
+      </c>
+      <c r="N76" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="T76" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>500</v>
+      </c>
+      <c r="E77" t="n">
+        <v>500</v>
+      </c>
+      <c r="F77" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G77" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4289</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4289</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4289</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>256</v>
+      </c>
+      <c r="N77" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>160.52</v>
+      </c>
+      <c r="R77" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="S77" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="T77" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>50</v>
+      </c>
+      <c r="E78" t="n">
+        <v>50</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H78" t="n">
+        <v>282</v>
+      </c>
+      <c r="I78" t="n">
+        <v>282</v>
+      </c>
+      <c r="J78" t="n">
+        <v>282</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>256</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>152.39</v>
+      </c>
+      <c r="R78" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="S78" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="T78" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C79" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>250</v>
+      </c>
+      <c r="E79" t="n">
+        <v>250</v>
+      </c>
+      <c r="F79" t="n">
+        <v>62500</v>
+      </c>
+      <c r="G79" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2182</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2182</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2182</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>256</v>
+      </c>
+      <c r="N79" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>249.27</v>
+      </c>
+      <c r="R79" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="S79" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="T79" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
